--- a/utils/Backup_Checker/backup_config.xlsx
+++ b/utils/Backup_Checker/backup_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://phenomenetworks-my.sharepoint.com/personal/itay-b_phenomenetworks_onmicrosoft_com/Documents/Laptop_Documents/GitHub/scripts/utils/Backup_Checker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{06BF08A4-A50F-4ED7-A0FC-6A974502048A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2454251E-B1B3-49BA-B8EE-77D7DC1B5C77}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{06BF08A4-A50F-4ED7-A0FC-6A974502048A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8964802-ECD7-40F6-B017-EF3CFC0E6D8C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1389,7 +1389,7 @@
         <v>s3://phenome-bat-mysql-weekly-backup/weekly_backups/</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
